--- a/data/trans_orig/IP07_A12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A12_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6120</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2431</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12203</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7139</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3236</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12531</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13181</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28794</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19521</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38104</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22536</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15995</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33529</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20212</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40199</t>
+          <t>28231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51936</t>
+          <t>49483</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40105</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66491</t>
+          <t>61784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>115577</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105311</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>126581</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>91458</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>80518</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>100739</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>125332</t>
+          <t>93138</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113624</t>
+          <t>83924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135554</t>
+          <t>101380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>216791</t>
+          <t>208714</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199990</t>
+          <t>194528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231307</t>
+          <t>221918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>161237</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>161237</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>161237</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>130472</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>130472</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>130472</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>130801</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>130801</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>130801</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>171327</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>171327</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>171327</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>371</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>301799</t>
+          <t>292037</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>301799</t>
+          <t>292037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>301799</t>
+          <t>292037</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11820</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7838</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13798</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5996</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4123</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10018</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1543</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16902</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10436</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26465</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>12192</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6460</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19481</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>33987</t>
+          <t>29848</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53592</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>48071</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35408</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64906</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>35520</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23654</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>48119</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49849</t>
+          <t>36980</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36893</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70063</t>
+          <t>47937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>85369</t>
+          <t>85052</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66298</t>
+          <t>69006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>107412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>186614</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>168750</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>200969</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>179007</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>164119</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>197136</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>190058</t>
+          <t>162043</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168898</t>
+          <t>150327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>207487</t>
+          <t>173998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>369065</t>
+          <t>348657</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342839</t>
+          <t>326156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>395786</t>
+          <t>367805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>258747</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>258747</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>258747</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>238680</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>238680</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>238680</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>224653</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>224653</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>224653</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>268398</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>268398</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>268398</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>593</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>507077</t>
+          <t>483400</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>507077</t>
+          <t>483400</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>507077</t>
+          <t>483400</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11270</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5845</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19657</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14977</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9075</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23044</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17479</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11959</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3486</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>13845</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23637</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15174</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33778</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>18326</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11385</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26668</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49434</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34783</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68958</t>
+          <t>57482</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>76865</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>61815</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>97418</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>58055</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>43418</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>72831</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>79250</t>
+          <t>57670</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63174</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101345</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>137305</t>
+          <t>134535</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115800</t>
+          <t>114712</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>163058</t>
+          <t>156284</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>302191</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>278960</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>319865</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>71,95%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>66,42%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>270465</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>253007</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>295159</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>68,54%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>315390</t>
+          <t>255180</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>289031</t>
+          <t>240268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>336001</t>
+          <t>269836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>585855</t>
+          <t>557371</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>555292</t>
+          <t>533483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615138</t>
+          <t>581580</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>355453</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>355453</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>355453</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>439724</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>439724</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>439724</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>964</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
